--- a/Result/profitability/1506.xlsx
+++ b/Result/profitability/1506.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00625000000000003</v>
+        <v>-0.006249999999999971</v>
       </c>
       <c r="N2" t="n">
-        <v>16.455</v>
+        <v>16.295</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>-0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06999999999999997</v>
+        <v>-0.08249999999999996</v>
       </c>
       <c r="N3" t="n">
-        <v>16.75625</v>
+        <v>15.54</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.14375</v>
+        <v>-0.1525</v>
       </c>
       <c r="N4" t="n">
-        <v>16.00125</v>
+        <v>15.21125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.20875</v>
+        <v>-0.21125</v>
       </c>
       <c r="N5" t="n">
-        <v>16.09125</v>
+        <v>15.3175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.23625</v>
+        <v>-0.25375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.745</v>
+        <v>13.51625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.275</v>
+        <v>-0.285</v>
       </c>
       <c r="N7" t="n">
-        <v>14.09</v>
+        <v>13.34</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.77</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.37375</v>
+        <v>-0.38375</v>
       </c>
       <c r="N8" t="n">
-        <v>12.93875</v>
+        <v>12.1675</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>326</v>
+      </c>
+      <c r="D75" t="n">
+        <v>289</v>
+      </c>
+      <c r="E75" t="n">
+        <v>37</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.01375000000000003</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.170000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3537844036697249</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.190000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3545246277205041</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
